--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="148">
   <si>
     <t>sid</t>
   </si>
@@ -515,7 +515,13 @@
     <t>狼月</t>
   </si>
   <si>
+    <t>Wolfmoon</t>
+  </si>
+  <si>
     <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>MahjongWays2</t>
   </si>
   <si>
     <t>糖果派对</t>
@@ -7484,7 +7490,9 @@
       <c r="E122" s="5">
         <v>101500001</v>
       </c>
-      <c r="F122" s="5"/>
+      <c r="F122" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G122" s="1" t="s">
         <v>32</v>
       </c>
@@ -7529,7 +7537,9 @@
       <c r="E123" s="5">
         <v>101500001</v>
       </c>
-      <c r="F123" s="5"/>
+      <c r="F123" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G123" s="1" t="s">
         <v>35</v>
       </c>
@@ -7574,7 +7584,9 @@
       <c r="E124" s="5">
         <v>101500001</v>
       </c>
-      <c r="F124" s="5"/>
+      <c r="F124" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G124" s="1" t="s">
         <v>36</v>
       </c>
@@ -7614,12 +7626,14 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E125" s="5">
         <v>105300001</v>
       </c>
-      <c r="F125" s="5"/>
+      <c r="F125" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G125" s="1" t="s">
         <v>32</v>
       </c>
@@ -7659,12 +7673,14 @@
         <v>1</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E126" s="5">
         <v>105300001</v>
       </c>
-      <c r="F126" s="5"/>
+      <c r="F126" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G126" s="1" t="s">
         <v>35</v>
       </c>
@@ -7704,12 +7720,14 @@
         <v>1</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E127" s="5">
         <v>105300001</v>
       </c>
-      <c r="F127" s="5"/>
+      <c r="F127" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G127" s="1" t="s">
         <v>36</v>
       </c>
@@ -7749,13 +7767,13 @@
         <v>1</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E128" s="5">
         <v>105100001</v>
       </c>
       <c r="F128" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>32</v>
@@ -7796,13 +7814,13 @@
         <v>1</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E129" s="5">
         <v>105100001</v>
       </c>
       <c r="F129" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>35</v>
@@ -7843,13 +7861,13 @@
         <v>1</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E130" s="5">
         <v>105100001</v>
       </c>
       <c r="F130" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>36</v>
@@ -7890,13 +7908,13 @@
         <v>1</v>
       </c>
       <c r="D131" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E131" s="24">
         <v>105500001</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>32</v>
@@ -7937,13 +7955,13 @@
         <v>1</v>
       </c>
       <c r="D132" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E132" s="24">
         <v>105500001</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>35</v>
@@ -7984,13 +8002,13 @@
         <v>1</v>
       </c>
       <c r="D133" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E133" s="24">
         <v>105500001</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>36</v>
@@ -8031,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E134" s="24">
         <v>105501001</v>
@@ -8076,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E135" s="24">
         <v>105501001</v>
@@ -8121,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E136" s="24">
         <v>105501001</v>
@@ -8166,7 +8184,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E137" s="24">
         <v>105502001</v>
@@ -8211,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E138" s="24">
         <v>105502001</v>
@@ -8256,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E139" s="24">
         <v>105502001</v>
@@ -8301,13 +8319,13 @@
         <v>4</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E140" s="26">
         <v>400400001</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>32</v>
@@ -8325,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M140" s="33" t="s">
         <v>34</v>
@@ -8348,13 +8366,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E141" s="26">
         <v>400200001</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>32</v>
@@ -8372,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M141" s="33" t="s">
         <v>34</v>
@@ -8395,13 +8413,13 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E142" s="26">
         <v>400500001</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>32</v>
@@ -8419,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M142" s="33" t="s">
         <v>34</v>
@@ -8442,13 +8460,13 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E143" s="26">
         <v>400700001</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>32</v>
@@ -8466,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M143" s="33" t="s">
         <v>34</v>
@@ -8498,7 +8516,7 @@
         <v>78</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H144" s="18">
         <v>10</v>
@@ -8513,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M144" s="18">
         <v>0</v>
@@ -8545,7 +8563,7 @@
         <v>78</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H145" s="18">
         <v>11</v>
@@ -8560,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M145" s="18">
         <v>0</v>
@@ -8592,7 +8610,7 @@
         <v>78</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H146" s="18">
         <v>12</v>
@@ -8607,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M146" s="18">
         <v>0</v>
@@ -8639,7 +8657,7 @@
         <v>80</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H147" s="18">
         <v>10</v>
@@ -8654,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M147" s="18">
         <v>0</v>
@@ -8686,7 +8704,7 @@
         <v>80</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H148" s="18">
         <v>11</v>
@@ -8701,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M148" s="18">
         <v>0</v>
@@ -8733,7 +8751,7 @@
         <v>80</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H149" s="18">
         <v>12</v>
@@ -8748,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M149" s="18">
         <v>0</v>
@@ -8780,7 +8798,7 @@
         <v>82</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H150" s="18">
         <v>10</v>
@@ -8795,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M150" s="18">
         <v>0</v>
@@ -8827,7 +8845,7 @@
         <v>82</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H151" s="18">
         <v>11</v>
@@ -8842,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M151" s="18">
         <v>0</v>
@@ -8874,7 +8892,7 @@
         <v>82</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H152" s="18">
         <v>12</v>
@@ -8889,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M152" s="18">
         <v>0</v>
@@ -8921,7 +8939,7 @@
         <v>84</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H153" s="18">
         <v>10</v>
@@ -8936,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M153" s="18">
         <v>0</v>
@@ -8968,7 +8986,7 @@
         <v>84</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H154" s="18">
         <v>11</v>
@@ -8983,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M154" s="18">
         <v>0</v>
@@ -9015,7 +9033,7 @@
         <v>84</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H155" s="18">
         <v>12</v>
@@ -9030,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M155" s="18">
         <v>0</v>
@@ -9062,7 +9080,7 @@
         <v>86</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H156" s="18">
         <v>10</v>
@@ -9077,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M156" s="18">
         <v>0</v>
@@ -9109,7 +9127,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H157" s="18">
         <v>11</v>
@@ -9124,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M157" s="18">
         <v>0</v>
@@ -9156,7 +9174,7 @@
         <v>86</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H158" s="18">
         <v>12</v>
@@ -9171,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M158" s="18">
         <v>0</v>
@@ -9203,7 +9221,7 @@
         <v>89</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H159" s="18">
         <v>10</v>
@@ -9218,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M159" s="18">
         <v>0</v>
@@ -9250,7 +9268,7 @@
         <v>89</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H160" s="18">
         <v>11</v>
@@ -9265,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M160" s="18">
         <v>0</v>
@@ -9297,7 +9315,7 @@
         <v>89</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H161" s="18">
         <v>12</v>
@@ -9312,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M161" s="18">
         <v>0</v>
@@ -9344,7 +9362,7 @@
         <v>91</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H162" s="18">
         <v>10</v>
@@ -9359,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M162" s="18">
         <v>0</v>
@@ -9391,7 +9409,7 @@
         <v>91</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H163" s="18">
         <v>11</v>
@@ -9406,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M163" s="18">
         <v>0</v>
@@ -9438,7 +9456,7 @@
         <v>91</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H164" s="18">
         <v>12</v>
@@ -9453,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M164" s="18">
         <v>0</v>
@@ -9485,7 +9503,7 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H165" s="18">
         <v>10</v>
@@ -9500,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M165" s="18">
         <v>0</v>
@@ -9532,7 +9550,7 @@
         <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H166" s="18">
         <v>11</v>
@@ -9547,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M166" s="18">
         <v>0</v>
@@ -9579,7 +9597,7 @@
         <v>93</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H167" s="18">
         <v>12</v>
@@ -9594,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M167" s="18">
         <v>0</v>
@@ -9626,7 +9644,7 @@
         <v>95</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H168" s="18">
         <v>10</v>
@@ -9641,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M168" s="18">
         <v>0</v>
@@ -9673,7 +9691,7 @@
         <v>95</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H169" s="18">
         <v>11</v>
@@ -9688,7 +9706,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M169" s="18">
         <v>0</v>
@@ -9720,7 +9738,7 @@
         <v>95</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H170" s="18">
         <v>12</v>
@@ -9735,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M170" s="18">
         <v>0</v>
@@ -9767,7 +9785,7 @@
         <v>101</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H171" s="18">
         <v>10</v>
@@ -9782,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M171" s="18">
         <v>0</v>
@@ -9814,7 +9832,7 @@
         <v>101</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H172" s="18">
         <v>11</v>
@@ -9829,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M172" s="18">
         <v>0</v>
@@ -9861,7 +9879,7 @@
         <v>101</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H173" s="18">
         <v>12</v>
@@ -9876,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M173" s="18">
         <v>0</v>
@@ -9908,7 +9926,7 @@
         <v>104</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H174" s="18">
         <v>10</v>
@@ -9923,7 +9941,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M174" s="18">
         <v>0</v>
@@ -9956,7 +9974,7 @@
         <v>104</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H175" s="18">
         <v>11</v>
@@ -9971,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M175" s="18">
         <v>0</v>
@@ -10004,7 +10022,7 @@
         <v>104</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H176" s="18">
         <v>12</v>
@@ -10019,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M176" s="18">
         <v>0</v>
@@ -10052,7 +10070,7 @@
         <v>107</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H177" s="18">
         <v>10</v>
@@ -10067,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M177" s="18">
         <v>0</v>
@@ -10100,7 +10118,7 @@
         <v>107</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H178" s="18">
         <v>11</v>
@@ -10115,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M178" s="18">
         <v>0</v>
@@ -10148,7 +10166,7 @@
         <v>107</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H179" s="18">
         <v>12</v>
@@ -10163,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M179" s="18">
         <v>0</v>
@@ -10196,7 +10214,7 @@
         <v>109</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H180" s="18">
         <v>10</v>
@@ -10211,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M180" s="18">
         <v>0</v>
@@ -10244,7 +10262,7 @@
         <v>109</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H181" s="18">
         <v>11</v>
@@ -10259,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M181" s="18">
         <v>0</v>
@@ -10292,7 +10310,7 @@
         <v>109</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H182" s="18">
         <v>12</v>
@@ -10307,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M182" s="18">
         <v>0</v>
@@ -10341,7 +10359,7 @@
         <v>31</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H183" s="18">
         <v>10</v>
@@ -10356,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M183" s="18">
         <v>0</v>
@@ -10390,7 +10408,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H184" s="18">
         <v>11</v>
@@ -10405,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M184" s="18">
         <v>0</v>
@@ -10439,7 +10457,7 @@
         <v>31</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H185" s="18">
         <v>12</v>
@@ -10454,7 +10472,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M185" s="18">
         <v>0</v>
@@ -10487,7 +10505,7 @@
         <v>38</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H186" s="18">
         <v>10</v>
@@ -10502,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M186" s="18">
         <v>0</v>
@@ -10537,7 +10555,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H187" s="18">
         <v>11</v>
@@ -10552,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M187" s="18">
         <v>0</v>
@@ -10587,7 +10605,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H188" s="18">
         <v>12</v>
@@ -10602,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -10635,7 +10653,7 @@
         <v>40</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H189" s="18">
         <v>10</v>
@@ -10650,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M189" s="18">
         <v>0</v>
@@ -10685,7 +10703,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H190" s="18">
         <v>11</v>
@@ -10700,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M190" s="18">
         <v>0</v>
@@ -10735,7 +10753,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H191" s="18">
         <v>12</v>
@@ -10750,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M191" s="18">
         <v>0</v>
@@ -10783,7 +10801,7 @@
         <v>42</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H192" s="18">
         <v>10</v>
@@ -10798,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -10833,7 +10851,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H193" s="18">
         <v>11</v>
@@ -10848,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M193" s="18">
         <v>0</v>
@@ -10883,7 +10901,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H194" s="18">
         <v>12</v>
@@ -10898,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M194" s="18">
         <v>0</v>
@@ -10931,7 +10949,7 @@
         <v>44</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H195" s="18">
         <v>10</v>
@@ -10946,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -10981,7 +10999,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H196" s="18">
         <v>11</v>
@@ -10996,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M196" s="18">
         <v>0</v>
@@ -11031,7 +11049,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H197" s="18">
         <v>12</v>
@@ -11046,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M197" s="18">
         <v>0</v>
@@ -11079,7 +11097,7 @@
         <v>46</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H198" s="18">
         <v>10</v>
@@ -11094,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M198" s="18">
         <v>0</v>
@@ -11128,7 +11146,7 @@
         <v>46</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H199" s="18">
         <v>11</v>
@@ -11143,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M199" s="18">
         <v>0</v>
@@ -11177,7 +11195,7 @@
         <v>46</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H200" s="18">
         <v>12</v>
@@ -11192,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M200" s="18">
         <v>0</v>
@@ -11225,7 +11243,7 @@
         <v>48</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H201" s="18">
         <v>10</v>
@@ -11240,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -11273,7 +11291,7 @@
         <v>48</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H202" s="18">
         <v>11</v>
@@ -11288,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M202" s="18">
         <v>0</v>
@@ -11321,7 +11339,7 @@
         <v>48</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H203" s="18">
         <v>12</v>
@@ -11336,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M203" s="18">
         <v>0</v>
@@ -11369,7 +11387,7 @@
         <v>50</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H204" s="18">
         <v>10</v>
@@ -11384,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
@@ -11417,7 +11435,7 @@
         <v>50</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H205" s="18">
         <v>11</v>
@@ -11432,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M205" s="18">
         <v>0</v>
@@ -11465,7 +11483,7 @@
         <v>50</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H206" s="18">
         <v>12</v>
@@ -11480,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M206" s="18">
         <v>0</v>
@@ -11513,7 +11531,7 @@
         <v>52</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H207" s="18">
         <v>10</v>
@@ -11528,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M207" s="18">
         <v>0</v>
@@ -11561,7 +11579,7 @@
         <v>52</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H208" s="18">
         <v>11</v>
@@ -11576,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M208" s="18">
         <v>0</v>
@@ -11609,7 +11627,7 @@
         <v>52</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H209" s="18">
         <v>12</v>
@@ -11624,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M209" s="18">
         <v>0</v>
@@ -11657,7 +11675,7 @@
         <v>54</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H210" s="18">
         <v>10</v>
@@ -11672,7 +11690,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M210" s="18">
         <v>0</v>
@@ -11705,7 +11723,7 @@
         <v>54</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H211" s="18">
         <v>11</v>
@@ -11720,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M211" s="18">
         <v>0</v>
@@ -11753,7 +11771,7 @@
         <v>54</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H212" s="18">
         <v>12</v>
@@ -11768,7 +11786,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M212" s="18">
         <v>0</v>
@@ -11801,7 +11819,7 @@
         <v>56</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H213" s="18">
         <v>10</v>
@@ -11816,7 +11834,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M213" s="18">
         <v>0</v>
@@ -11849,7 +11867,7 @@
         <v>56</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H214" s="18">
         <v>11</v>
@@ -11864,7 +11882,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M214" s="18">
         <v>0</v>
@@ -11897,7 +11915,7 @@
         <v>56</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H215" s="18">
         <v>12</v>
@@ -11912,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M215" s="18">
         <v>0</v>
@@ -11945,7 +11963,7 @@
         <v>58</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H216" s="18">
         <v>10</v>
@@ -11960,7 +11978,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -11993,7 +12011,7 @@
         <v>58</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H217" s="18">
         <v>11</v>
@@ -12008,7 +12026,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M217" s="18">
         <v>0</v>
@@ -12041,7 +12059,7 @@
         <v>58</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H218" s="18">
         <v>12</v>
@@ -12056,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M218" s="18">
         <v>0</v>
@@ -12089,7 +12107,7 @@
         <v>60</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H219" s="1">
         <v>10</v>
@@ -12104,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M219" s="18">
         <v>0</v>
@@ -12137,7 +12155,7 @@
         <v>60</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H220" s="1">
         <v>11</v>
@@ -12152,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M220" s="18">
         <v>0</v>
@@ -12185,7 +12203,7 @@
         <v>60</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H221" s="1">
         <v>12</v>
@@ -12200,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M221" s="18">
         <v>0</v>
@@ -12233,7 +12251,7 @@
         <v>62</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H222" s="1">
         <v>10</v>
@@ -12248,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M222" s="18">
         <v>0</v>
@@ -12281,7 +12299,7 @@
         <v>62</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H223" s="1">
         <v>11</v>
@@ -12296,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M223" s="18">
         <v>0</v>
@@ -12329,7 +12347,7 @@
         <v>62</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H224" s="1">
         <v>12</v>
@@ -12344,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M224" s="18">
         <v>0</v>
@@ -12377,7 +12395,7 @@
         <v>64</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H225" s="1">
         <v>10</v>
@@ -12392,7 +12410,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M225" s="18">
         <v>0</v>
@@ -12425,7 +12443,7 @@
         <v>64</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H226" s="1">
         <v>11</v>
@@ -12440,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M226" s="18">
         <v>0</v>
@@ -12473,7 +12491,7 @@
         <v>64</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H227" s="1">
         <v>12</v>
@@ -12488,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M227" s="18">
         <v>0</v>
@@ -12521,7 +12539,7 @@
         <v>66</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H228" s="1">
         <v>10</v>
@@ -12536,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M228" s="18">
         <v>0</v>
@@ -12569,7 +12587,7 @@
         <v>66</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H229" s="1">
         <v>11</v>
@@ -12584,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M229" s="18">
         <v>0</v>
@@ -12617,7 +12635,7 @@
         <v>66</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H230" s="1">
         <v>12</v>
@@ -12632,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M230" s="18">
         <v>0</v>
@@ -12665,7 +12683,7 @@
         <v>68</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H231" s="1">
         <v>10</v>
@@ -12680,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M231" s="18">
         <v>0</v>
@@ -12713,7 +12731,7 @@
         <v>68</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H232" s="1">
         <v>11</v>
@@ -12728,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M232" s="18">
         <v>0</v>
@@ -12761,7 +12779,7 @@
         <v>68</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H233" s="1">
         <v>12</v>
@@ -12776,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M233" s="18">
         <v>0</v>
@@ -12809,7 +12827,7 @@
         <v>70</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H234" s="1">
         <v>10</v>
@@ -12824,7 +12842,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M234" s="18">
         <v>0</v>
@@ -12857,7 +12875,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H235" s="1">
         <v>11</v>
@@ -12872,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M235" s="18">
         <v>0</v>
@@ -12905,7 +12923,7 @@
         <v>70</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H236" s="1">
         <v>12</v>
@@ -12920,7 +12938,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M236" s="18">
         <v>0</v>
@@ -12952,7 +12970,7 @@
         <v>72</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H237" s="1">
         <v>10</v>
@@ -12967,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M237" s="18">
         <v>0</v>
@@ -12999,7 +13017,7 @@
         <v>72</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H238" s="1">
         <v>11</v>
@@ -13014,7 +13032,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M238" s="18">
         <v>0</v>
@@ -13046,7 +13064,7 @@
         <v>72</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H239" s="1">
         <v>12</v>
@@ -13061,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M239" s="18">
         <v>0</v>
@@ -13093,7 +13111,7 @@
         <v>74</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H240" s="1">
         <v>10</v>
@@ -13108,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M240" s="18">
         <v>0</v>
@@ -13140,7 +13158,7 @@
         <v>74</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H241" s="1">
         <v>11</v>
@@ -13155,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M241" s="18">
         <v>0</v>
@@ -13187,7 +13205,7 @@
         <v>74</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H242" s="1">
         <v>12</v>
@@ -13202,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M242" s="18">
         <v>0</v>
@@ -13234,7 +13252,7 @@
         <v>76</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H243" s="1">
         <v>10</v>
@@ -13249,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M243" s="18">
         <v>0</v>
@@ -13282,7 +13300,7 @@
         <v>76</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H244" s="1">
         <v>11</v>
@@ -13297,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M244" s="18">
         <v>0</v>
@@ -13330,7 +13348,7 @@
         <v>76</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H245" s="1">
         <v>12</v>
@@ -13345,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M245" s="18">
         <v>0</v>
@@ -13378,7 +13396,7 @@
         <v>111</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H246" s="1">
         <v>10</v>
@@ -13393,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M246" s="18">
         <v>0</v>
@@ -13425,7 +13443,7 @@
         <v>111</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H247" s="1">
         <v>11</v>
@@ -13440,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M247" s="18">
         <v>0</v>
@@ -13472,7 +13490,7 @@
         <v>111</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H248" s="1">
         <v>12</v>
@@ -13487,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M248" s="18">
         <v>0</v>
@@ -13519,7 +13537,7 @@
         <v>113</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H249" s="1">
         <v>10</v>
@@ -13534,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M249" s="18">
         <v>0</v>
@@ -13566,7 +13584,7 @@
         <v>113</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H250" s="1">
         <v>11</v>
@@ -13581,7 +13599,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M250" s="18">
         <v>0</v>
@@ -13613,7 +13631,7 @@
         <v>113</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H251" s="1">
         <v>12</v>
@@ -13628,7 +13646,7 @@
         <v>0</v>
       </c>
       <c r="L251" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M251" s="18">
         <v>0</v>
@@ -13660,7 +13678,7 @@
         <v>115</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H252" s="1">
         <v>10</v>
@@ -13675,7 +13693,7 @@
         <v>0</v>
       </c>
       <c r="L252" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M252" s="18">
         <v>0</v>
@@ -13707,7 +13725,7 @@
         <v>115</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H253" s="1">
         <v>11</v>
@@ -13722,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="L253" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M253" s="18">
         <v>0</v>
@@ -13754,7 +13772,7 @@
         <v>115</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H254" s="1">
         <v>12</v>
@@ -13769,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="L254" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M254" s="18">
         <v>0</v>
@@ -13797,9 +13815,11 @@
       <c r="E255" s="5">
         <v>103900001</v>
       </c>
-      <c r="F255" s="5"/>
+      <c r="F255" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G255" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H255" s="1">
         <v>10</v>
@@ -13814,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M255" s="18">
         <v>0</v>
@@ -13842,9 +13862,11 @@
       <c r="E256" s="5">
         <v>103900001</v>
       </c>
-      <c r="F256" s="5"/>
+      <c r="F256" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G256" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H256" s="1">
         <v>11</v>
@@ -13859,7 +13881,7 @@
         <v>0</v>
       </c>
       <c r="L256" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M256" s="18">
         <v>0</v>
@@ -13887,9 +13909,11 @@
       <c r="E257" s="5">
         <v>103900001</v>
       </c>
-      <c r="F257" s="5"/>
+      <c r="F257" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G257" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H257" s="1">
         <v>12</v>
@@ -13904,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M257" s="18">
         <v>0</v>
@@ -13932,9 +13956,11 @@
       <c r="E258" s="5">
         <v>101500001</v>
       </c>
-      <c r="F258" s="5"/>
+      <c r="F258" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G258" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H258" s="1">
         <v>10</v>
@@ -13949,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M258" s="18">
         <v>0</v>
@@ -13977,9 +14003,11 @@
       <c r="E259" s="5">
         <v>101500001</v>
       </c>
-      <c r="F259" s="5"/>
+      <c r="F259" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G259" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H259" s="1">
         <v>11</v>
@@ -13994,7 +14022,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M259" s="18">
         <v>0</v>
@@ -14022,9 +14050,11 @@
       <c r="E260" s="5">
         <v>101500001</v>
       </c>
-      <c r="F260" s="5"/>
+      <c r="F260" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G260" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H260" s="1">
         <v>12</v>
@@ -14039,7 +14069,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M260" s="18">
         <v>0</v>
@@ -14062,14 +14092,16 @@
         <v>1</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E261" s="5">
         <v>105300001</v>
       </c>
-      <c r="F261" s="5"/>
+      <c r="F261" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G261" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H261" s="1">
         <v>10</v>
@@ -14084,7 +14116,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M261" s="18">
         <v>0</v>
@@ -14107,14 +14139,16 @@
         <v>1</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E262" s="5">
         <v>105300001</v>
       </c>
-      <c r="F262" s="5"/>
+      <c r="F262" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G262" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H262" s="1">
         <v>11</v>
@@ -14129,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M262" s="18">
         <v>0</v>
@@ -14152,14 +14186,16 @@
         <v>1</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E263" s="5">
         <v>105300001</v>
       </c>
-      <c r="F263" s="5"/>
+      <c r="F263" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G263" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H263" s="1">
         <v>12</v>
@@ -14174,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M263" s="18">
         <v>0</v>
@@ -14197,16 +14233,16 @@
         <v>1</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E264" s="5">
         <v>105100001</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H264" s="1">
         <v>10</v>
@@ -14221,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M264" s="18">
         <v>0</v>
@@ -14244,16 +14280,16 @@
         <v>1</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E265" s="5">
         <v>105100001</v>
       </c>
       <c r="F265" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H265" s="1">
         <v>11</v>
@@ -14268,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M265" s="18">
         <v>0</v>
@@ -14291,16 +14327,16 @@
         <v>1</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E266" s="5">
         <v>105100001</v>
       </c>
       <c r="F266" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H266" s="1">
         <v>12</v>
@@ -14315,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M266" s="18">
         <v>0</v>
@@ -14338,16 +14374,16 @@
         <v>1</v>
       </c>
       <c r="D267" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E267" s="2">
         <v>105500001</v>
       </c>
       <c r="F267" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G267" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H267" s="2">
         <v>10</v>
@@ -14362,7 +14398,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M267" s="30">
         <v>0</v>
@@ -14389,16 +14425,16 @@
         <v>1</v>
       </c>
       <c r="D268" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E268" s="2">
         <v>105500001</v>
       </c>
       <c r="F268" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G268" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H268" s="2">
         <v>11</v>
@@ -14413,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M268" s="30">
         <v>0</v>
@@ -14440,16 +14476,16 @@
         <v>1</v>
       </c>
       <c r="D269" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E269" s="2">
         <v>105500001</v>
       </c>
       <c r="F269" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G269" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H269" s="2">
         <v>12</v>
@@ -14464,7 +14500,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M269" s="30">
         <v>0</v>
@@ -14491,14 +14527,14 @@
         <v>1</v>
       </c>
       <c r="D270" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E270" s="2">
         <v>105501001</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H270" s="2">
         <v>10</v>
@@ -14513,7 +14549,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M270" s="30">
         <v>0</v>
@@ -14540,14 +14576,14 @@
         <v>1</v>
       </c>
       <c r="D271" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E271" s="2">
         <v>105501001</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H271" s="2">
         <v>11</v>
@@ -14562,7 +14598,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M271" s="30">
         <v>0</v>
@@ -14589,14 +14625,14 @@
         <v>1</v>
       </c>
       <c r="D272" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E272" s="2">
         <v>105501001</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H272" s="2">
         <v>12</v>
@@ -14611,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M272" s="30">
         <v>0</v>
@@ -14638,14 +14674,14 @@
         <v>1</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E273" s="2">
         <v>105502001</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H273" s="2">
         <v>10</v>
@@ -14660,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M273" s="30">
         <v>0</v>
@@ -14687,14 +14723,14 @@
         <v>1</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E274" s="2">
         <v>105502001</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H274" s="2">
         <v>11</v>
@@ -14709,7 +14745,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M274" s="30">
         <v>0</v>
@@ -14736,14 +14772,14 @@
         <v>1</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E275" s="2">
         <v>105502001</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H275" s="2">
         <v>12</v>
@@ -14758,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M275" s="30">
         <v>0</v>
@@ -14794,7 +14830,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H276" s="1">
         <v>21</v>
@@ -14842,7 +14878,7 @@
         <v>31</v>
       </c>
       <c r="G277" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H277" s="1">
         <v>22</v>
@@ -14890,7 +14926,7 @@
         <v>31</v>
       </c>
       <c r="G278" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H278" s="1">
         <v>23</v>
@@ -14938,7 +14974,7 @@
         <v>38</v>
       </c>
       <c r="G279" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H279" s="1">
         <v>21</v>
@@ -14986,7 +15022,7 @@
         <v>38</v>
       </c>
       <c r="G280" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H280" s="1">
         <v>22</v>
@@ -15034,7 +15070,7 @@
         <v>38</v>
       </c>
       <c r="G281" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H281" s="1">
         <v>23</v>
@@ -15082,7 +15118,7 @@
         <v>40</v>
       </c>
       <c r="G282" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H282" s="1">
         <v>21</v>
@@ -15130,7 +15166,7 @@
         <v>40</v>
       </c>
       <c r="G283" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H283" s="1">
         <v>22</v>
@@ -15178,7 +15214,7 @@
         <v>40</v>
       </c>
       <c r="G284" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H284" s="1">
         <v>23</v>
@@ -15226,7 +15262,7 @@
         <v>42</v>
       </c>
       <c r="G285" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H285" s="1">
         <v>21</v>
@@ -15274,7 +15310,7 @@
         <v>42</v>
       </c>
       <c r="G286" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H286" s="1">
         <v>22</v>
@@ -15322,7 +15358,7 @@
         <v>42</v>
       </c>
       <c r="G287" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H287" s="1">
         <v>23</v>
@@ -15370,7 +15406,7 @@
         <v>44</v>
       </c>
       <c r="G288" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H288" s="1">
         <v>21</v>
@@ -15418,7 +15454,7 @@
         <v>44</v>
       </c>
       <c r="G289" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H289" s="1">
         <v>22</v>
@@ -15466,7 +15502,7 @@
         <v>44</v>
       </c>
       <c r="G290" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H290" s="1">
         <v>23</v>
@@ -15514,7 +15550,7 @@
         <v>46</v>
       </c>
       <c r="G291" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H291" s="1">
         <v>21</v>
@@ -15562,7 +15598,7 @@
         <v>46</v>
       </c>
       <c r="G292" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H292" s="1">
         <v>22</v>
@@ -15610,7 +15646,7 @@
         <v>46</v>
       </c>
       <c r="G293" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H293" s="1">
         <v>23</v>
@@ -15658,7 +15694,7 @@
         <v>48</v>
       </c>
       <c r="G294" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H294" s="1">
         <v>21</v>
@@ -15706,7 +15742,7 @@
         <v>48</v>
       </c>
       <c r="G295" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H295" s="1">
         <v>22</v>
@@ -15754,7 +15790,7 @@
         <v>48</v>
       </c>
       <c r="G296" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H296" s="1">
         <v>23</v>
@@ -15802,7 +15838,7 @@
         <v>50</v>
       </c>
       <c r="G297" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H297" s="1">
         <v>21</v>
@@ -15850,7 +15886,7 @@
         <v>50</v>
       </c>
       <c r="G298" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H298" s="1">
         <v>22</v>
@@ -15898,7 +15934,7 @@
         <v>50</v>
       </c>
       <c r="G299" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H299" s="1">
         <v>23</v>
@@ -15946,7 +15982,7 @@
         <v>52</v>
       </c>
       <c r="G300" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H300" s="1">
         <v>21</v>
@@ -15994,7 +16030,7 @@
         <v>52</v>
       </c>
       <c r="G301" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H301" s="1">
         <v>22</v>
@@ -16042,7 +16078,7 @@
         <v>52</v>
       </c>
       <c r="G302" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H302" s="1">
         <v>23</v>
@@ -16091,7 +16127,7 @@
         <v>54</v>
       </c>
       <c r="G303" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H303" s="1">
         <v>21</v>
@@ -16140,7 +16176,7 @@
         <v>54</v>
       </c>
       <c r="G304" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H304" s="1">
         <v>22</v>
@@ -16189,7 +16225,7 @@
         <v>54</v>
       </c>
       <c r="G305" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H305" s="1">
         <v>23</v>
@@ -16238,7 +16274,7 @@
         <v>56</v>
       </c>
       <c r="G306" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H306" s="1">
         <v>21</v>
@@ -16287,7 +16323,7 @@
         <v>56</v>
       </c>
       <c r="G307" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H307" s="1">
         <v>22</v>
@@ -16336,7 +16372,7 @@
         <v>56</v>
       </c>
       <c r="G308" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H308" s="1">
         <v>23</v>
@@ -16385,7 +16421,7 @@
         <v>58</v>
       </c>
       <c r="G309" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H309" s="1">
         <v>21</v>
@@ -16434,7 +16470,7 @@
         <v>58</v>
       </c>
       <c r="G310" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H310" s="1">
         <v>22</v>
@@ -16483,7 +16519,7 @@
         <v>58</v>
       </c>
       <c r="G311" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H311" s="1">
         <v>23</v>
@@ -16531,7 +16567,7 @@
         <v>60</v>
       </c>
       <c r="G312" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H312" s="1">
         <v>21</v>
@@ -16579,7 +16615,7 @@
         <v>60</v>
       </c>
       <c r="G313" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H313" s="1">
         <v>22</v>
@@ -16627,7 +16663,7 @@
         <v>60</v>
       </c>
       <c r="G314" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H314" s="1">
         <v>23</v>
@@ -16676,7 +16712,7 @@
         <v>62</v>
       </c>
       <c r="G315" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H315" s="1">
         <v>21</v>
@@ -16725,7 +16761,7 @@
         <v>62</v>
       </c>
       <c r="G316" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H316" s="1">
         <v>22</v>
@@ -16774,7 +16810,7 @@
         <v>62</v>
       </c>
       <c r="G317" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H317" s="1">
         <v>23</v>
@@ -16822,7 +16858,7 @@
         <v>64</v>
       </c>
       <c r="G318" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H318" s="1">
         <v>21</v>
@@ -16870,7 +16906,7 @@
         <v>64</v>
       </c>
       <c r="G319" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H319" s="1">
         <v>22</v>
@@ -16918,7 +16954,7 @@
         <v>64</v>
       </c>
       <c r="G320" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H320" s="1">
         <v>23</v>
@@ -16966,7 +17002,7 @@
         <v>66</v>
       </c>
       <c r="G321" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H321" s="1">
         <v>21</v>
@@ -17014,7 +17050,7 @@
         <v>66</v>
       </c>
       <c r="G322" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H322" s="1">
         <v>22</v>
@@ -17062,7 +17098,7 @@
         <v>66</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H323" s="1">
         <v>23</v>
@@ -17111,7 +17147,7 @@
         <v>68</v>
       </c>
       <c r="G324" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H324" s="1">
         <v>21</v>
@@ -17160,7 +17196,7 @@
         <v>68</v>
       </c>
       <c r="G325" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H325" s="1">
         <v>22</v>
@@ -17209,7 +17245,7 @@
         <v>68</v>
       </c>
       <c r="G326" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H326" s="1">
         <v>23</v>
@@ -17257,7 +17293,7 @@
         <v>72</v>
       </c>
       <c r="G327" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H327" s="1">
         <v>21</v>
@@ -17305,7 +17341,7 @@
         <v>72</v>
       </c>
       <c r="G328" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H328" s="1">
         <v>22</v>
@@ -17353,7 +17389,7 @@
         <v>72</v>
       </c>
       <c r="G329" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H329" s="1">
         <v>23</v>
@@ -17401,7 +17437,7 @@
         <v>74</v>
       </c>
       <c r="G330" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H330" s="1">
         <v>21</v>
@@ -17449,7 +17485,7 @@
         <v>74</v>
       </c>
       <c r="G331" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H331" s="1">
         <v>22</v>
@@ -17497,7 +17533,7 @@
         <v>74</v>
       </c>
       <c r="G332" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H332" s="1">
         <v>23</v>
@@ -17545,7 +17581,7 @@
         <v>76</v>
       </c>
       <c r="G333" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H333" s="1">
         <v>21</v>
@@ -17593,7 +17629,7 @@
         <v>76</v>
       </c>
       <c r="G334" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H334" s="1">
         <v>22</v>
@@ -17641,7 +17677,7 @@
         <v>76</v>
       </c>
       <c r="G335" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H335" s="1">
         <v>23</v>
@@ -19145,13 +19181,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E366" s="14">
         <v>300402001</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>32</v>
@@ -19194,13 +19230,13 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E367" s="14">
         <v>300402001</v>
       </c>
       <c r="F367" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>35</v>
@@ -19243,13 +19279,13 @@
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E368" s="14">
         <v>300402001</v>
       </c>
       <c r="F368" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>36</v>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -8310,7 +8310,7 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" s="25">
-        <v>4004001</v>
+        <v>4004004</v>
       </c>
       <c r="B140" s="25">
         <v>400400</v>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="2">
-        <v>4002001</v>
+        <v>4002004</v>
       </c>
       <c r="B141" s="2">
         <v>400200</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="2">
-        <v>4005001</v>
+        <v>4005004</v>
       </c>
       <c r="B142" s="2">
         <v>400500</v>
@@ -8451,7 +8451,7 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="2">
-        <v>4007001</v>
+        <v>4007004</v>
       </c>
       <c r="B143" s="2">
         <v>400700</v>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="150">
   <si>
     <t>sid</t>
   </si>
@@ -539,7 +539,13 @@
     <t>伽罗宝石1</t>
   </si>
   <si>
+    <t>GaloGemstone2</t>
+  </si>
+  <si>
     <t>伽罗宝石2</t>
+  </si>
+  <si>
+    <t>GaloGemstone3</t>
   </si>
   <si>
     <t>空袭</t>
@@ -8054,7 +8060,9 @@
       <c r="E134" s="24">
         <v>105501001</v>
       </c>
-      <c r="F134" s="24"/>
+      <c r="F134" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G134" s="1" t="s">
         <v>32</v>
       </c>
@@ -8099,7 +8107,9 @@
       <c r="E135" s="24">
         <v>105501001</v>
       </c>
-      <c r="F135" s="24"/>
+      <c r="F135" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G135" s="1" t="s">
         <v>35</v>
       </c>
@@ -8144,7 +8154,9 @@
       <c r="E136" s="24">
         <v>105501001</v>
       </c>
-      <c r="F136" s="24"/>
+      <c r="F136" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G136" s="1" t="s">
         <v>36</v>
       </c>
@@ -8184,12 +8196,14 @@
         <v>1</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E137" s="24">
         <v>105502001</v>
       </c>
-      <c r="F137" s="24"/>
+      <c r="F137" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G137" s="1" t="s">
         <v>32</v>
       </c>
@@ -8229,12 +8243,14 @@
         <v>1</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E138" s="24">
         <v>105502001</v>
       </c>
-      <c r="F138" s="24"/>
+      <c r="F138" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G138" s="1" t="s">
         <v>35</v>
       </c>
@@ -8274,12 +8290,14 @@
         <v>1</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E139" s="24">
         <v>105502001</v>
       </c>
-      <c r="F139" s="24"/>
+      <c r="F139" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G139" s="1" t="s">
         <v>36</v>
       </c>
@@ -8319,13 +8337,13 @@
         <v>4</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E140" s="26">
         <v>400400001</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>32</v>
@@ -8343,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M140" s="33" t="s">
         <v>34</v>
@@ -8366,13 +8384,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E141" s="26">
         <v>400200001</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>32</v>
@@ -8390,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M141" s="33" t="s">
         <v>34</v>
@@ -8413,13 +8431,13 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E142" s="26">
         <v>400500001</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>32</v>
@@ -8437,7 +8455,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M142" s="33" t="s">
         <v>34</v>
@@ -8460,13 +8478,13 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E143" s="26">
         <v>400700001</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>32</v>
@@ -8484,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M143" s="33" t="s">
         <v>34</v>
@@ -8516,7 +8534,7 @@
         <v>78</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H144" s="18">
         <v>10</v>
@@ -8531,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M144" s="18">
         <v>0</v>
@@ -8563,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H145" s="18">
         <v>11</v>
@@ -8578,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M145" s="18">
         <v>0</v>
@@ -8610,7 +8628,7 @@
         <v>78</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H146" s="18">
         <v>12</v>
@@ -8625,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M146" s="18">
         <v>0</v>
@@ -8657,7 +8675,7 @@
         <v>80</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H147" s="18">
         <v>10</v>
@@ -8672,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M147" s="18">
         <v>0</v>
@@ -8704,7 +8722,7 @@
         <v>80</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H148" s="18">
         <v>11</v>
@@ -8719,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M148" s="18">
         <v>0</v>
@@ -8751,7 +8769,7 @@
         <v>80</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H149" s="18">
         <v>12</v>
@@ -8766,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M149" s="18">
         <v>0</v>
@@ -8798,7 +8816,7 @@
         <v>82</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H150" s="18">
         <v>10</v>
@@ -8813,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M150" s="18">
         <v>0</v>
@@ -8845,7 +8863,7 @@
         <v>82</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H151" s="18">
         <v>11</v>
@@ -8860,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M151" s="18">
         <v>0</v>
@@ -8892,7 +8910,7 @@
         <v>82</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H152" s="18">
         <v>12</v>
@@ -8907,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M152" s="18">
         <v>0</v>
@@ -8939,7 +8957,7 @@
         <v>84</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H153" s="18">
         <v>10</v>
@@ -8954,7 +8972,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M153" s="18">
         <v>0</v>
@@ -8986,7 +9004,7 @@
         <v>84</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H154" s="18">
         <v>11</v>
@@ -9001,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M154" s="18">
         <v>0</v>
@@ -9033,7 +9051,7 @@
         <v>84</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H155" s="18">
         <v>12</v>
@@ -9048,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M155" s="18">
         <v>0</v>
@@ -9080,7 +9098,7 @@
         <v>86</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H156" s="18">
         <v>10</v>
@@ -9095,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M156" s="18">
         <v>0</v>
@@ -9127,7 +9145,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H157" s="18">
         <v>11</v>
@@ -9142,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M157" s="18">
         <v>0</v>
@@ -9174,7 +9192,7 @@
         <v>86</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H158" s="18">
         <v>12</v>
@@ -9189,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M158" s="18">
         <v>0</v>
@@ -9221,7 +9239,7 @@
         <v>89</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H159" s="18">
         <v>10</v>
@@ -9236,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M159" s="18">
         <v>0</v>
@@ -9268,7 +9286,7 @@
         <v>89</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H160" s="18">
         <v>11</v>
@@ -9283,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M160" s="18">
         <v>0</v>
@@ -9315,7 +9333,7 @@
         <v>89</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H161" s="18">
         <v>12</v>
@@ -9330,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M161" s="18">
         <v>0</v>
@@ -9362,7 +9380,7 @@
         <v>91</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H162" s="18">
         <v>10</v>
@@ -9377,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M162" s="18">
         <v>0</v>
@@ -9409,7 +9427,7 @@
         <v>91</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H163" s="18">
         <v>11</v>
@@ -9424,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M163" s="18">
         <v>0</v>
@@ -9456,7 +9474,7 @@
         <v>91</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H164" s="18">
         <v>12</v>
@@ -9471,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M164" s="18">
         <v>0</v>
@@ -9503,7 +9521,7 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H165" s="18">
         <v>10</v>
@@ -9518,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M165" s="18">
         <v>0</v>
@@ -9550,7 +9568,7 @@
         <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H166" s="18">
         <v>11</v>
@@ -9565,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M166" s="18">
         <v>0</v>
@@ -9597,7 +9615,7 @@
         <v>93</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H167" s="18">
         <v>12</v>
@@ -9612,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M167" s="18">
         <v>0</v>
@@ -9644,7 +9662,7 @@
         <v>95</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H168" s="18">
         <v>10</v>
@@ -9659,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M168" s="18">
         <v>0</v>
@@ -9691,7 +9709,7 @@
         <v>95</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H169" s="18">
         <v>11</v>
@@ -9706,7 +9724,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M169" s="18">
         <v>0</v>
@@ -9738,7 +9756,7 @@
         <v>95</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H170" s="18">
         <v>12</v>
@@ -9753,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M170" s="18">
         <v>0</v>
@@ -9785,7 +9803,7 @@
         <v>101</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H171" s="18">
         <v>10</v>
@@ -9800,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M171" s="18">
         <v>0</v>
@@ -9832,7 +9850,7 @@
         <v>101</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H172" s="18">
         <v>11</v>
@@ -9847,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M172" s="18">
         <v>0</v>
@@ -9879,7 +9897,7 @@
         <v>101</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H173" s="18">
         <v>12</v>
@@ -9894,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M173" s="18">
         <v>0</v>
@@ -9926,7 +9944,7 @@
         <v>104</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H174" s="18">
         <v>10</v>
@@ -9941,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M174" s="18">
         <v>0</v>
@@ -9974,7 +9992,7 @@
         <v>104</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H175" s="18">
         <v>11</v>
@@ -9989,7 +10007,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M175" s="18">
         <v>0</v>
@@ -10022,7 +10040,7 @@
         <v>104</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H176" s="18">
         <v>12</v>
@@ -10037,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M176" s="18">
         <v>0</v>
@@ -10070,7 +10088,7 @@
         <v>107</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H177" s="18">
         <v>10</v>
@@ -10085,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M177" s="18">
         <v>0</v>
@@ -10118,7 +10136,7 @@
         <v>107</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H178" s="18">
         <v>11</v>
@@ -10133,7 +10151,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M178" s="18">
         <v>0</v>
@@ -10166,7 +10184,7 @@
         <v>107</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H179" s="18">
         <v>12</v>
@@ -10181,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M179" s="18">
         <v>0</v>
@@ -10214,7 +10232,7 @@
         <v>109</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H180" s="18">
         <v>10</v>
@@ -10229,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M180" s="18">
         <v>0</v>
@@ -10262,7 +10280,7 @@
         <v>109</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H181" s="18">
         <v>11</v>
@@ -10277,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M181" s="18">
         <v>0</v>
@@ -10310,7 +10328,7 @@
         <v>109</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H182" s="18">
         <v>12</v>
@@ -10325,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M182" s="18">
         <v>0</v>
@@ -10359,7 +10377,7 @@
         <v>31</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H183" s="18">
         <v>10</v>
@@ -10374,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M183" s="18">
         <v>0</v>
@@ -10408,7 +10426,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H184" s="18">
         <v>11</v>
@@ -10423,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M184" s="18">
         <v>0</v>
@@ -10457,7 +10475,7 @@
         <v>31</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H185" s="18">
         <v>12</v>
@@ -10472,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M185" s="18">
         <v>0</v>
@@ -10505,7 +10523,7 @@
         <v>38</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H186" s="18">
         <v>10</v>
@@ -10520,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M186" s="18">
         <v>0</v>
@@ -10555,7 +10573,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H187" s="18">
         <v>11</v>
@@ -10570,7 +10588,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M187" s="18">
         <v>0</v>
@@ -10605,7 +10623,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H188" s="18">
         <v>12</v>
@@ -10620,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -10653,7 +10671,7 @@
         <v>40</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H189" s="18">
         <v>10</v>
@@ -10668,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M189" s="18">
         <v>0</v>
@@ -10703,7 +10721,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H190" s="18">
         <v>11</v>
@@ -10718,7 +10736,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M190" s="18">
         <v>0</v>
@@ -10753,7 +10771,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H191" s="18">
         <v>12</v>
@@ -10768,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M191" s="18">
         <v>0</v>
@@ -10801,7 +10819,7 @@
         <v>42</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H192" s="18">
         <v>10</v>
@@ -10816,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -10851,7 +10869,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H193" s="18">
         <v>11</v>
@@ -10866,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M193" s="18">
         <v>0</v>
@@ -10901,7 +10919,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H194" s="18">
         <v>12</v>
@@ -10916,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M194" s="18">
         <v>0</v>
@@ -10949,7 +10967,7 @@
         <v>44</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H195" s="18">
         <v>10</v>
@@ -10964,7 +10982,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -10999,7 +11017,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H196" s="18">
         <v>11</v>
@@ -11014,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M196" s="18">
         <v>0</v>
@@ -11049,7 +11067,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H197" s="18">
         <v>12</v>
@@ -11064,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M197" s="18">
         <v>0</v>
@@ -11097,7 +11115,7 @@
         <v>46</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H198" s="18">
         <v>10</v>
@@ -11112,7 +11130,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M198" s="18">
         <v>0</v>
@@ -11146,7 +11164,7 @@
         <v>46</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H199" s="18">
         <v>11</v>
@@ -11161,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M199" s="18">
         <v>0</v>
@@ -11195,7 +11213,7 @@
         <v>46</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H200" s="18">
         <v>12</v>
@@ -11210,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M200" s="18">
         <v>0</v>
@@ -11243,7 +11261,7 @@
         <v>48</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H201" s="18">
         <v>10</v>
@@ -11258,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -11291,7 +11309,7 @@
         <v>48</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H202" s="18">
         <v>11</v>
@@ -11306,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M202" s="18">
         <v>0</v>
@@ -11339,7 +11357,7 @@
         <v>48</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H203" s="18">
         <v>12</v>
@@ -11354,7 +11372,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M203" s="18">
         <v>0</v>
@@ -11387,7 +11405,7 @@
         <v>50</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H204" s="18">
         <v>10</v>
@@ -11402,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
@@ -11435,7 +11453,7 @@
         <v>50</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H205" s="18">
         <v>11</v>
@@ -11450,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M205" s="18">
         <v>0</v>
@@ -11483,7 +11501,7 @@
         <v>50</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H206" s="18">
         <v>12</v>
@@ -11498,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M206" s="18">
         <v>0</v>
@@ -11531,7 +11549,7 @@
         <v>52</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H207" s="18">
         <v>10</v>
@@ -11546,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M207" s="18">
         <v>0</v>
@@ -11579,7 +11597,7 @@
         <v>52</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H208" s="18">
         <v>11</v>
@@ -11594,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M208" s="18">
         <v>0</v>
@@ -11627,7 +11645,7 @@
         <v>52</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H209" s="18">
         <v>12</v>
@@ -11642,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M209" s="18">
         <v>0</v>
@@ -11675,7 +11693,7 @@
         <v>54</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H210" s="18">
         <v>10</v>
@@ -11690,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M210" s="18">
         <v>0</v>
@@ -11723,7 +11741,7 @@
         <v>54</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H211" s="18">
         <v>11</v>
@@ -11738,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M211" s="18">
         <v>0</v>
@@ -11771,7 +11789,7 @@
         <v>54</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H212" s="18">
         <v>12</v>
@@ -11786,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M212" s="18">
         <v>0</v>
@@ -11819,7 +11837,7 @@
         <v>56</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H213" s="18">
         <v>10</v>
@@ -11834,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M213" s="18">
         <v>0</v>
@@ -11867,7 +11885,7 @@
         <v>56</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H214" s="18">
         <v>11</v>
@@ -11882,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M214" s="18">
         <v>0</v>
@@ -11915,7 +11933,7 @@
         <v>56</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H215" s="18">
         <v>12</v>
@@ -11930,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M215" s="18">
         <v>0</v>
@@ -11963,7 +11981,7 @@
         <v>58</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H216" s="18">
         <v>10</v>
@@ -11978,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -12011,7 +12029,7 @@
         <v>58</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H217" s="18">
         <v>11</v>
@@ -12026,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M217" s="18">
         <v>0</v>
@@ -12059,7 +12077,7 @@
         <v>58</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H218" s="18">
         <v>12</v>
@@ -12074,7 +12092,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M218" s="18">
         <v>0</v>
@@ -12107,7 +12125,7 @@
         <v>60</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H219" s="1">
         <v>10</v>
@@ -12122,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M219" s="18">
         <v>0</v>
@@ -12155,7 +12173,7 @@
         <v>60</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H220" s="1">
         <v>11</v>
@@ -12170,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M220" s="18">
         <v>0</v>
@@ -12203,7 +12221,7 @@
         <v>60</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H221" s="1">
         <v>12</v>
@@ -12218,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M221" s="18">
         <v>0</v>
@@ -12251,7 +12269,7 @@
         <v>62</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H222" s="1">
         <v>10</v>
@@ -12266,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M222" s="18">
         <v>0</v>
@@ -12299,7 +12317,7 @@
         <v>62</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H223" s="1">
         <v>11</v>
@@ -12314,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M223" s="18">
         <v>0</v>
@@ -12347,7 +12365,7 @@
         <v>62</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H224" s="1">
         <v>12</v>
@@ -12362,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M224" s="18">
         <v>0</v>
@@ -12395,7 +12413,7 @@
         <v>64</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H225" s="1">
         <v>10</v>
@@ -12410,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M225" s="18">
         <v>0</v>
@@ -12443,7 +12461,7 @@
         <v>64</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H226" s="1">
         <v>11</v>
@@ -12458,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M226" s="18">
         <v>0</v>
@@ -12491,7 +12509,7 @@
         <v>64</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H227" s="1">
         <v>12</v>
@@ -12506,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M227" s="18">
         <v>0</v>
@@ -12539,7 +12557,7 @@
         <v>66</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H228" s="1">
         <v>10</v>
@@ -12554,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M228" s="18">
         <v>0</v>
@@ -12587,7 +12605,7 @@
         <v>66</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H229" s="1">
         <v>11</v>
@@ -12602,7 +12620,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M229" s="18">
         <v>0</v>
@@ -12635,7 +12653,7 @@
         <v>66</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H230" s="1">
         <v>12</v>
@@ -12650,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M230" s="18">
         <v>0</v>
@@ -12683,7 +12701,7 @@
         <v>68</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H231" s="1">
         <v>10</v>
@@ -12698,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M231" s="18">
         <v>0</v>
@@ -12731,7 +12749,7 @@
         <v>68</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H232" s="1">
         <v>11</v>
@@ -12746,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M232" s="18">
         <v>0</v>
@@ -12779,7 +12797,7 @@
         <v>68</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H233" s="1">
         <v>12</v>
@@ -12794,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M233" s="18">
         <v>0</v>
@@ -12827,7 +12845,7 @@
         <v>70</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H234" s="1">
         <v>10</v>
@@ -12842,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M234" s="18">
         <v>0</v>
@@ -12875,7 +12893,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H235" s="1">
         <v>11</v>
@@ -12890,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M235" s="18">
         <v>0</v>
@@ -12923,7 +12941,7 @@
         <v>70</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H236" s="1">
         <v>12</v>
@@ -12938,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M236" s="18">
         <v>0</v>
@@ -12970,7 +12988,7 @@
         <v>72</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H237" s="1">
         <v>10</v>
@@ -12985,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M237" s="18">
         <v>0</v>
@@ -13017,7 +13035,7 @@
         <v>72</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H238" s="1">
         <v>11</v>
@@ -13032,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M238" s="18">
         <v>0</v>
@@ -13064,7 +13082,7 @@
         <v>72</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H239" s="1">
         <v>12</v>
@@ -13079,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M239" s="18">
         <v>0</v>
@@ -13111,7 +13129,7 @@
         <v>74</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H240" s="1">
         <v>10</v>
@@ -13126,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M240" s="18">
         <v>0</v>
@@ -13158,7 +13176,7 @@
         <v>74</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H241" s="1">
         <v>11</v>
@@ -13173,7 +13191,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M241" s="18">
         <v>0</v>
@@ -13205,7 +13223,7 @@
         <v>74</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H242" s="1">
         <v>12</v>
@@ -13220,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M242" s="18">
         <v>0</v>
@@ -13252,7 +13270,7 @@
         <v>76</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H243" s="1">
         <v>10</v>
@@ -13267,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M243" s="18">
         <v>0</v>
@@ -13300,7 +13318,7 @@
         <v>76</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H244" s="1">
         <v>11</v>
@@ -13315,7 +13333,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M244" s="18">
         <v>0</v>
@@ -13348,7 +13366,7 @@
         <v>76</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H245" s="1">
         <v>12</v>
@@ -13363,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M245" s="18">
         <v>0</v>
@@ -13396,7 +13414,7 @@
         <v>111</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H246" s="1">
         <v>10</v>
@@ -13411,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M246" s="18">
         <v>0</v>
@@ -13443,7 +13461,7 @@
         <v>111</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H247" s="1">
         <v>11</v>
@@ -13458,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M247" s="18">
         <v>0</v>
@@ -13490,7 +13508,7 @@
         <v>111</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H248" s="1">
         <v>12</v>
@@ -13505,7 +13523,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M248" s="18">
         <v>0</v>
@@ -13537,7 +13555,7 @@
         <v>113</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H249" s="1">
         <v>10</v>
@@ -13552,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M249" s="18">
         <v>0</v>
@@ -13584,7 +13602,7 @@
         <v>113</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H250" s="1">
         <v>11</v>
@@ -13599,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M250" s="18">
         <v>0</v>
@@ -13631,7 +13649,7 @@
         <v>113</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H251" s="1">
         <v>12</v>
@@ -13646,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="L251" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M251" s="18">
         <v>0</v>
@@ -13678,7 +13696,7 @@
         <v>115</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H252" s="1">
         <v>10</v>
@@ -13693,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="L252" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M252" s="18">
         <v>0</v>
@@ -13725,7 +13743,7 @@
         <v>115</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H253" s="1">
         <v>11</v>
@@ -13740,7 +13758,7 @@
         <v>0</v>
       </c>
       <c r="L253" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M253" s="18">
         <v>0</v>
@@ -13772,7 +13790,7 @@
         <v>115</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H254" s="1">
         <v>12</v>
@@ -13787,7 +13805,7 @@
         <v>0</v>
       </c>
       <c r="L254" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M254" s="18">
         <v>0</v>
@@ -13819,7 +13837,7 @@
         <v>117</v>
       </c>
       <c r="G255" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H255" s="1">
         <v>10</v>
@@ -13834,7 +13852,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M255" s="18">
         <v>0</v>
@@ -13866,7 +13884,7 @@
         <v>117</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H256" s="1">
         <v>11</v>
@@ -13881,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L256" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M256" s="18">
         <v>0</v>
@@ -13913,7 +13931,7 @@
         <v>117</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H257" s="1">
         <v>12</v>
@@ -13928,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M257" s="18">
         <v>0</v>
@@ -13960,7 +13978,7 @@
         <v>119</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H258" s="1">
         <v>10</v>
@@ -13975,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M258" s="18">
         <v>0</v>
@@ -14007,7 +14025,7 @@
         <v>119</v>
       </c>
       <c r="G259" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H259" s="1">
         <v>11</v>
@@ -14022,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M259" s="18">
         <v>0</v>
@@ -14054,7 +14072,7 @@
         <v>119</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H260" s="1">
         <v>12</v>
@@ -14069,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M260" s="18">
         <v>0</v>
@@ -14101,7 +14119,7 @@
         <v>121</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H261" s="1">
         <v>10</v>
@@ -14116,7 +14134,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M261" s="18">
         <v>0</v>
@@ -14148,7 +14166,7 @@
         <v>121</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H262" s="1">
         <v>11</v>
@@ -14163,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M262" s="18">
         <v>0</v>
@@ -14195,7 +14213,7 @@
         <v>121</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H263" s="1">
         <v>12</v>
@@ -14210,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M263" s="18">
         <v>0</v>
@@ -14242,7 +14260,7 @@
         <v>123</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H264" s="1">
         <v>10</v>
@@ -14257,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M264" s="18">
         <v>0</v>
@@ -14289,7 +14307,7 @@
         <v>123</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H265" s="1">
         <v>11</v>
@@ -14304,7 +14322,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M265" s="18">
         <v>0</v>
@@ -14336,7 +14354,7 @@
         <v>123</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H266" s="1">
         <v>12</v>
@@ -14351,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M266" s="18">
         <v>0</v>
@@ -14383,7 +14401,7 @@
         <v>125</v>
       </c>
       <c r="G267" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H267" s="2">
         <v>10</v>
@@ -14398,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M267" s="30">
         <v>0</v>
@@ -14434,7 +14452,7 @@
         <v>125</v>
       </c>
       <c r="G268" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H268" s="2">
         <v>11</v>
@@ -14449,7 +14467,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M268" s="30">
         <v>0</v>
@@ -14485,7 +14503,7 @@
         <v>125</v>
       </c>
       <c r="G269" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H269" s="2">
         <v>12</v>
@@ -14500,7 +14518,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M269" s="30">
         <v>0</v>
@@ -14532,9 +14550,11 @@
       <c r="E270" s="2">
         <v>105501001</v>
       </c>
-      <c r="F270" s="2"/>
+      <c r="F270" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G270" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H270" s="2">
         <v>10</v>
@@ -14549,7 +14569,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M270" s="30">
         <v>0</v>
@@ -14581,9 +14601,11 @@
       <c r="E271" s="2">
         <v>105501001</v>
       </c>
-      <c r="F271" s="2"/>
+      <c r="F271" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G271" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H271" s="2">
         <v>11</v>
@@ -14598,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M271" s="30">
         <v>0</v>
@@ -14630,9 +14652,11 @@
       <c r="E272" s="2">
         <v>105501001</v>
       </c>
-      <c r="F272" s="2"/>
+      <c r="F272" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G272" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H272" s="2">
         <v>12</v>
@@ -14647,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M272" s="30">
         <v>0</v>
@@ -14674,14 +14698,16 @@
         <v>1</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E273" s="2">
         <v>105502001</v>
       </c>
-      <c r="F273" s="2"/>
+      <c r="F273" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G273" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H273" s="2">
         <v>10</v>
@@ -14696,7 +14722,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M273" s="30">
         <v>0</v>
@@ -14723,14 +14749,16 @@
         <v>1</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E274" s="2">
         <v>105502001</v>
       </c>
-      <c r="F274" s="2"/>
+      <c r="F274" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G274" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H274" s="2">
         <v>11</v>
@@ -14745,7 +14773,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M274" s="30">
         <v>0</v>
@@ -14772,14 +14800,16 @@
         <v>1</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E275" s="2">
         <v>105502001</v>
       </c>
-      <c r="F275" s="2"/>
+      <c r="F275" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G275" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H275" s="2">
         <v>12</v>
@@ -14794,7 +14824,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M275" s="30">
         <v>0</v>
@@ -14830,7 +14860,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H276" s="1">
         <v>21</v>
@@ -14878,7 +14908,7 @@
         <v>31</v>
       </c>
       <c r="G277" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H277" s="1">
         <v>22</v>
@@ -14926,7 +14956,7 @@
         <v>31</v>
       </c>
       <c r="G278" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H278" s="1">
         <v>23</v>
@@ -14974,7 +15004,7 @@
         <v>38</v>
       </c>
       <c r="G279" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H279" s="1">
         <v>21</v>
@@ -15022,7 +15052,7 @@
         <v>38</v>
       </c>
       <c r="G280" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H280" s="1">
         <v>22</v>
@@ -15070,7 +15100,7 @@
         <v>38</v>
       </c>
       <c r="G281" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H281" s="1">
         <v>23</v>
@@ -15118,7 +15148,7 @@
         <v>40</v>
       </c>
       <c r="G282" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H282" s="1">
         <v>21</v>
@@ -15166,7 +15196,7 @@
         <v>40</v>
       </c>
       <c r="G283" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H283" s="1">
         <v>22</v>
@@ -15214,7 +15244,7 @@
         <v>40</v>
       </c>
       <c r="G284" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H284" s="1">
         <v>23</v>
@@ -15262,7 +15292,7 @@
         <v>42</v>
       </c>
       <c r="G285" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H285" s="1">
         <v>21</v>
@@ -15310,7 +15340,7 @@
         <v>42</v>
       </c>
       <c r="G286" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H286" s="1">
         <v>22</v>
@@ -15358,7 +15388,7 @@
         <v>42</v>
       </c>
       <c r="G287" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H287" s="1">
         <v>23</v>
@@ -15406,7 +15436,7 @@
         <v>44</v>
       </c>
       <c r="G288" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H288" s="1">
         <v>21</v>
@@ -15454,7 +15484,7 @@
         <v>44</v>
       </c>
       <c r="G289" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H289" s="1">
         <v>22</v>
@@ -15502,7 +15532,7 @@
         <v>44</v>
       </c>
       <c r="G290" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H290" s="1">
         <v>23</v>
@@ -15550,7 +15580,7 @@
         <v>46</v>
       </c>
       <c r="G291" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H291" s="1">
         <v>21</v>
@@ -15598,7 +15628,7 @@
         <v>46</v>
       </c>
       <c r="G292" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H292" s="1">
         <v>22</v>
@@ -15646,7 +15676,7 @@
         <v>46</v>
       </c>
       <c r="G293" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H293" s="1">
         <v>23</v>
@@ -15694,7 +15724,7 @@
         <v>48</v>
       </c>
       <c r="G294" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H294" s="1">
         <v>21</v>
@@ -15742,7 +15772,7 @@
         <v>48</v>
       </c>
       <c r="G295" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H295" s="1">
         <v>22</v>
@@ -15790,7 +15820,7 @@
         <v>48</v>
       </c>
       <c r="G296" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H296" s="1">
         <v>23</v>
@@ -15838,7 +15868,7 @@
         <v>50</v>
       </c>
       <c r="G297" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H297" s="1">
         <v>21</v>
@@ -15886,7 +15916,7 @@
         <v>50</v>
       </c>
       <c r="G298" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H298" s="1">
         <v>22</v>
@@ -15934,7 +15964,7 @@
         <v>50</v>
       </c>
       <c r="G299" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H299" s="1">
         <v>23</v>
@@ -15982,7 +16012,7 @@
         <v>52</v>
       </c>
       <c r="G300" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H300" s="1">
         <v>21</v>
@@ -16030,7 +16060,7 @@
         <v>52</v>
       </c>
       <c r="G301" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H301" s="1">
         <v>22</v>
@@ -16078,7 +16108,7 @@
         <v>52</v>
       </c>
       <c r="G302" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H302" s="1">
         <v>23</v>
@@ -16127,7 +16157,7 @@
         <v>54</v>
       </c>
       <c r="G303" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H303" s="1">
         <v>21</v>
@@ -16176,7 +16206,7 @@
         <v>54</v>
       </c>
       <c r="G304" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H304" s="1">
         <v>22</v>
@@ -16225,7 +16255,7 @@
         <v>54</v>
       </c>
       <c r="G305" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H305" s="1">
         <v>23</v>
@@ -16274,7 +16304,7 @@
         <v>56</v>
       </c>
       <c r="G306" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H306" s="1">
         <v>21</v>
@@ -16323,7 +16353,7 @@
         <v>56</v>
       </c>
       <c r="G307" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H307" s="1">
         <v>22</v>
@@ -16372,7 +16402,7 @@
         <v>56</v>
       </c>
       <c r="G308" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H308" s="1">
         <v>23</v>
@@ -16421,7 +16451,7 @@
         <v>58</v>
       </c>
       <c r="G309" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H309" s="1">
         <v>21</v>
@@ -16470,7 +16500,7 @@
         <v>58</v>
       </c>
       <c r="G310" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H310" s="1">
         <v>22</v>
@@ -16519,7 +16549,7 @@
         <v>58</v>
       </c>
       <c r="G311" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H311" s="1">
         <v>23</v>
@@ -16567,7 +16597,7 @@
         <v>60</v>
       </c>
       <c r="G312" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H312" s="1">
         <v>21</v>
@@ -16615,7 +16645,7 @@
         <v>60</v>
       </c>
       <c r="G313" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H313" s="1">
         <v>22</v>
@@ -16663,7 +16693,7 @@
         <v>60</v>
       </c>
       <c r="G314" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H314" s="1">
         <v>23</v>
@@ -16712,7 +16742,7 @@
         <v>62</v>
       </c>
       <c r="G315" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H315" s="1">
         <v>21</v>
@@ -16761,7 +16791,7 @@
         <v>62</v>
       </c>
       <c r="G316" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H316" s="1">
         <v>22</v>
@@ -16810,7 +16840,7 @@
         <v>62</v>
       </c>
       <c r="G317" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H317" s="1">
         <v>23</v>
@@ -16858,7 +16888,7 @@
         <v>64</v>
       </c>
       <c r="G318" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H318" s="1">
         <v>21</v>
@@ -16906,7 +16936,7 @@
         <v>64</v>
       </c>
       <c r="G319" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H319" s="1">
         <v>22</v>
@@ -16954,7 +16984,7 @@
         <v>64</v>
       </c>
       <c r="G320" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H320" s="1">
         <v>23</v>
@@ -17002,7 +17032,7 @@
         <v>66</v>
       </c>
       <c r="G321" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H321" s="1">
         <v>21</v>
@@ -17050,7 +17080,7 @@
         <v>66</v>
       </c>
       <c r="G322" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H322" s="1">
         <v>22</v>
@@ -17098,7 +17128,7 @@
         <v>66</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H323" s="1">
         <v>23</v>
@@ -17147,7 +17177,7 @@
         <v>68</v>
       </c>
       <c r="G324" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H324" s="1">
         <v>21</v>
@@ -17196,7 +17226,7 @@
         <v>68</v>
       </c>
       <c r="G325" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H325" s="1">
         <v>22</v>
@@ -17245,7 +17275,7 @@
         <v>68</v>
       </c>
       <c r="G326" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H326" s="1">
         <v>23</v>
@@ -17293,7 +17323,7 @@
         <v>72</v>
       </c>
       <c r="G327" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H327" s="1">
         <v>21</v>
@@ -17341,7 +17371,7 @@
         <v>72</v>
       </c>
       <c r="G328" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H328" s="1">
         <v>22</v>
@@ -17389,7 +17419,7 @@
         <v>72</v>
       </c>
       <c r="G329" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H329" s="1">
         <v>23</v>
@@ -17437,7 +17467,7 @@
         <v>74</v>
       </c>
       <c r="G330" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H330" s="1">
         <v>21</v>
@@ -17485,7 +17515,7 @@
         <v>74</v>
       </c>
       <c r="G331" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H331" s="1">
         <v>22</v>
@@ -17533,7 +17563,7 @@
         <v>74</v>
       </c>
       <c r="G332" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H332" s="1">
         <v>23</v>
@@ -17581,7 +17611,7 @@
         <v>76</v>
       </c>
       <c r="G333" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H333" s="1">
         <v>21</v>
@@ -17629,7 +17659,7 @@
         <v>76</v>
       </c>
       <c r="G334" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H334" s="1">
         <v>22</v>
@@ -17677,7 +17707,7 @@
         <v>76</v>
       </c>
       <c r="G335" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H335" s="1">
         <v>23</v>
@@ -19181,13 +19211,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E366" s="14">
         <v>300402001</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>32</v>
@@ -19230,13 +19260,13 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E367" s="14">
         <v>300402001</v>
       </c>
       <c r="F367" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>35</v>
@@ -19279,13 +19309,13 @@
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E368" s="14">
         <v>300402001</v>
       </c>
       <c r="F368" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>36</v>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -13129,7 +13129,7 @@
         <v>71</v>
       </c>
       <c r="E240" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F240" s="14" t="s">
         <v>72</v>
@@ -13176,7 +13176,7 @@
         <v>71</v>
       </c>
       <c r="E241" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F241" s="14" t="s">
         <v>72</v>
@@ -13223,7 +13223,7 @@
         <v>71</v>
       </c>
       <c r="E242" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F242" s="14" t="s">
         <v>72</v>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -833,12 +833,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8714,7 +8714,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S147" s="3"/>
     </row>
@@ -8762,7 +8762,7 @@
         <v>1000</v>
       </c>
       <c r="O148" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S148" s="3"/>
     </row>
@@ -8810,7 +8810,7 @@
         <v>10000</v>
       </c>
       <c r="O149" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S149" s="3"/>
     </row>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -833,12 +833,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8696,10 +8696,10 @@
         <v>1</v>
       </c>
       <c r="I147" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J147" s="1">
-        <v>200000</v>
+        <v>-1</v>
       </c>
       <c r="K147" s="1">
         <v>0</v>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -8696,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="I147" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J147" s="1">
         <v>-1</v>
@@ -8714,7 +8719,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S147" s="3"/>
     </row>
@@ -8762,7 +8767,7 @@
         <v>1000</v>
       </c>
       <c r="O148" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S148" s="3"/>
     </row>
@@ -8810,7 +8815,7 @@
         <v>10000</v>
       </c>
       <c r="O149" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S149" s="3"/>
     </row>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -520,7 +520,7 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>Wolfmoon</t>
+    <t>WolfMoon</t>
   </si>
   <si>
     <t>麻将胡了2</t>

--- a/ploy/resources/sample/warehouse.xlsx
+++ b/ploy/resources/sample/warehouse.xlsx
@@ -8683,7 +8683,7 @@
     </row>
     <row r="147" s="1" customFormat="1" spans="1:19">
       <c r="A147" s="2">
-        <v>4008004</v>
+        <v>4008001</v>
       </c>
       <c r="B147" s="2">
         <v>400800</v>
